--- a/mode_docx_gen/pmi_ka/ksv2_modes/КСВ_5.xlsx
+++ b/mode_docx_gen/pmi_ka/ksv2_modes/КСВ_5.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -617,8 +617,8 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1095,11 +1095,11 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
